--- a/static/examples/sample_import.xlsx
+++ b/static/examples/sample_import.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="9">
   <si>
-    <t>URN:Tel</t>
+    <t>URN:whatsapp</t>
   </si>
   <si>
     <t>Name</t>
